--- a/src/attributions/attributions_ig_traj_473.xlsx
+++ b/src/attributions/attributions_ig_traj_473.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2682725975269131</v>
+        <v>0.05594444073490019</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01977690095418631</v>
+        <v>-0.02429728670152947</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09038262166248211</v>
+        <v>-0.01891998566807835</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3341528273191412</v>
+        <v>0.1337784305396512</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.05430119732885804</v>
+        <v>-0.06554137461321846</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1996674283444208</v>
+        <v>-0.02952614212451531</v>
       </c>
       <c r="S2" t="n">
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.108529972780371</v>
+        <v>0.01964186396201118</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,79 +1065,79 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01574640515178227</v>
+        <v>-0.03672136567243341</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.04408700508305108</v>
+        <v>-0.009356111031981407</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.07341657446626589</v>
+        <v>-0.03649183316732124</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.0845517747293146</v>
+        <v>-0.04866065170627848</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.02307591564958476</v>
+        <v>0.0194012469203322</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05213442257973992</v>
+        <v>0.02346246106581725</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.04302272431522494</v>
+        <v>-0.00418508096022598</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.03853407933229323</v>
+        <v>0.0005137974894286006</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4896695794239113</v>
+        <v>0.1654525792528848</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
@@ -1146,25 +1146,25 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2015774289275474</v>
+        <v>-0.03563146381519287</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.1371293976112065</v>
+        <v>-0.004741067374427019</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.04229421105866791</v>
+        <v>-0.01327254292658378</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.07405771232252568</v>
+        <v>-0.02850082061883174</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,109 +1182,109 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.09263424435346074</v>
+        <v>-0.03269261924956587</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.004804252352354105</v>
+        <v>0.02474054971160097</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.2438068078425708</v>
+        <v>0.07109139937385336</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.06005293806716802</v>
+        <v>0.02596807821748073</v>
       </c>
       <c r="BU2" t="n">
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2513986392413844</v>
+        <v>0.07203811931755397</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.03835553312086414</v>
+        <v>-0.02665265108412285</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.02427548558159727</v>
+        <v>-0.02027498783787833</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1144433392113149</v>
+        <v>-0.03737241472816218</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.0004342885424829577</v>
+        <v>0.01630812768860988</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.08158791307144295</v>
+        <v>0.02044512473327361</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.02622854807290311</v>
+        <v>-0.04000171163390267</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.06645998200639289</v>
+        <v>0.007271986830825765</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,67 +1293,67 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0002912287815524991</v>
+        <v>0.0152039542009986</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1166616526597946</v>
+        <v>-0.03787318712298524</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.006549985320306368</v>
+        <v>0.008445278603768203</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0616466481390015</v>
+        <v>0.02307058945636601</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1633494067087778</v>
+        <v>-0.07419443006488655</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07730767849089043</v>
+        <v>0.001361627141826887</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.05628482115492958</v>
+        <v>0.0008762262263269615</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.04279163045055343</v>
+        <v>-0.01759190880879189</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.06709745267918969</v>
+        <v>0.02219822683273712</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.02626663056452299</v>
+        <v>0.02526612915099889</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1866076604177509</v>
+        <v>-0.02036373513787316</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.004797424110921674</v>
+        <v>-0.02736306428898137</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.02499233504417023</v>
+        <v>0.004031355258379936</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.07684417826424668</v>
+        <v>-0.02466502255709599</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.05105118437940637</v>
+        <v>-0.009378350087756589</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,82 +1425,82 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.1189827385763879</v>
+        <v>0.01538192465931742</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.05412685492463296</v>
+        <v>-0.01668373484384308</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.03541208643356927</v>
+        <v>0.02168393670922476</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.03718760383942243</v>
+        <v>0.02903633707189543</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1223511697837261</v>
+        <v>-0.0515219108424983</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.003862346780378521</v>
+        <v>0.007690106389256188</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.05646652095331872</v>
+        <v>0.0203604569080952</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.01018497391528004</v>
+        <v>0.03848664990067693</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.05425726596268491</v>
+        <v>-0.00712472529855356</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
@@ -1509,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.02597636469465123</v>
+        <v>0.03316731016281685</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.00770393549181855</v>
+        <v>-0.01054580403178096</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,25 +1524,25 @@
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.007483873043272324</v>
+        <v>0.009853270562061298</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.03320812069304872</v>
+        <v>0.00420067167897189</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.08406264976535731</v>
+        <v>-0.02623293882541385</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.04234285774042472</v>
+        <v>-0.01137028124547423</v>
       </c>
     </row>
     <row r="3">
@@ -2709,52 +2709,52 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.329739404496266</v>
+        <v>0.003263077204211833</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03504119339422981</v>
+        <v>-0.00141124541409803</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1214288396130512</v>
+        <v>-0.001903932903192416</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3412800149898095</v>
+        <v>0.008201839509422824</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03264159447913256</v>
+        <v>-0.002458456938013587</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1524622182915165</v>
+        <v>-0.005303944343143558</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,22 +2763,22 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1396134035405333</v>
+        <v>-0.0001963971575844862</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.121758370148059</v>
+        <v>-0.002781195431642098</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.04321609503297651</v>
+        <v>0.000292488500808637</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2787,64 +2787,64 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1249471027082217</v>
+        <v>-0.002694396809160263</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.09290028588372584</v>
+        <v>-0.004323730278030581</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.009551449171841836</v>
+        <v>7.049812603438727e-05</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.05304893367817377</v>
+        <v>-0.0001650856995165801</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.02481576952397785</v>
+        <v>-0.0007273409743589906</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.03990594077420406</v>
+        <v>0.0002122882569461302</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.4300626958318378</v>
+        <v>0.009520455914579971</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
@@ -2853,25 +2853,25 @@
         <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1316586015883016</v>
+        <v>-0.0003327494094758217</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.2367618562604226</v>
+        <v>-0.0008573957930357617</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.05784729436501616</v>
+        <v>-0.001485765704116089</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.09655859131166444</v>
+        <v>-0.00169418577397984</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00491563656916791</v>
+        <v>-0.0007050559123389079</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.02380959970575595</v>
+        <v>0.00184817428507789</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.09058750890308123</v>
+        <v>0.005013564174328046</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.08088684170115074</v>
+        <v>-0.0006147831478624437</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1695629994592913</v>
+        <v>0.004109883164027381</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.07008340349157055</v>
+        <v>-0.0002793611321826788</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.09825368390091734</v>
+        <v>-0.0006123848832971336</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1188928319494688</v>
+        <v>-0.00127418146147072</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.006482807343268096</v>
+        <v>0.001108927738603325</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.06010730973889362</v>
+        <v>0.0006816021296241791</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2976,52 +2976,52 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.02166201910361254</v>
+        <v>-0.002246208018200478</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.08705587596693716</v>
+        <v>0.0002872643572640362</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.009381210141514478</v>
+        <v>-0.001071189521286152</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1109536867465582</v>
+        <v>-0.001456300316120994</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.02108524125789343</v>
+        <v>0.0004732112656040681</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.07456189657709507</v>
+        <v>0.001203547788199997</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1268480063285294</v>
+        <v>-0.001882818675699053</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,25 +3042,25 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.03279659136603739</v>
+        <v>-0.002471095883927755</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.02829375436085453</v>
+        <v>0.0004199770092343138</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.04475581583813636</v>
+        <v>0.0009291081293054114</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,40 +3069,40 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0213358570801968</v>
+        <v>0.0003532300287055361</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.01252080455758541</v>
+        <v>0.002048879782821627</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1441919400203852</v>
+        <v>-0.001957912492794864</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
         <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02075014540769405</v>
+        <v>-2.084679303106118e-05</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.02893493117181658</v>
+        <v>0.002371289937518807</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3111,10 +3111,10 @@
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04865431621836851</v>
+        <v>-0.0008700236727566316</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
@@ -3123,67 +3123,67 @@
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.01394573898531674</v>
+        <v>0.0004220162945058529</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0882705186318011</v>
+        <v>-9.592571562509059e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.08398383984308844</v>
+        <v>-0.0006408066115857127</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.06764021736642659</v>
+        <v>-0.0005292047213799167</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.05318502920887613</v>
+        <v>0.0006161138080700343</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1157774992794783</v>
+        <v>-0.001939576355301558</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02892773787120006</v>
+        <v>0.0002297484541733339</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.07841461717586996</v>
+        <v>0.0007967513740931445</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3195,61 +3195,61 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0006104521923067727</v>
+        <v>0.001679970174545311</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.03064759233492155</v>
+        <v>-0.001226227007651953</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.01270534177148304</v>
+        <v>-0.00156773301985587</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01185681879651032</v>
+        <v>-0.0001401093114917</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.003182770382763528</v>
+        <v>0.0003377663078263469</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.05014367255667615</v>
+        <v>0.002353560420768876</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.05286641408818149</v>
+        <v>-0.001000575343974719</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3258,19 +3258,19 @@
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.01026080957267931</v>
+        <v>0.002383249079096964</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3847,49 +3847,49 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5091494480061397</v>
+        <v>0.4136239349003106</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3485301208031067</v>
+        <v>-0.3754077310833911</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0284727737155516</v>
+        <v>0.01330022925948175</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4912127847526005</v>
+        <v>0.5790358217684737</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3587260694078647</v>
+        <v>-0.4402653029742247</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.09095316956961562</v>
+        <v>-0.04160277176488209</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2084676087803331</v>
+        <v>0.2117446107480994</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01990441044588038</v>
+        <v>-0.05002326023263757</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1507249135335912</v>
+        <v>-0.03743988325086713</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,52 +3925,52 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1343009941599115</v>
+        <v>-0.09198366000332278</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.002073694856067761</v>
+        <v>-0.1697350390120856</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.02020560601660971</v>
+        <v>-0.08193578748997662</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02014367858576904</v>
+        <v>0.2274003774121407</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1029768918859508</v>
+        <v>-0.08267936327576261</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06786753816092971</v>
+        <v>0.1512609015644746</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3982,16 +3982,16 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5691320961418292</v>
+        <v>0.5187743950038455</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.08734423935739968</v>
+        <v>-0.2964608275016288</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2112377287974646</v>
+        <v>-0.2153710375625711</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,25 +4000,25 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.04692878462369308</v>
+        <v>-0.07837199329312718</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1061724320203671</v>
+        <v>-0.1380618558739102</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1510069363401169</v>
+        <v>-0.08056900851986862</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4036,100 +4036,100 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04975314654346591</v>
+        <v>-0.09612382717522741</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.07218683978534621</v>
+        <v>0.08792684842113975</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.2159390774979577</v>
+        <v>-0.04932697812310359</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2324523010596126</v>
+        <v>0.4451729659264667</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.001483405045776278</v>
+        <v>-0.1777879068581754</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.118056094124087</v>
+        <v>-0.04167645792030682</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1498218073074595</v>
+        <v>-0.1848469213612891</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.04904232665161382</v>
+        <v>0.2186484815751139</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03456274985344952</v>
+        <v>-0.04875953207363614</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.003804926626583998</v>
+        <v>-0.1368883367421784</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.2024311154284203</v>
+        <v>0.4693771374260143</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1627437570133688</v>
+        <v>0.2421188198453166</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,28 +4138,28 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1413390853596127</v>
+        <v>-0.1824688616829477</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.08896554690536274</v>
+        <v>0.2256115121624319</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.0318980974198192</v>
+        <v>-0.02342287383185355</v>
       </c>
       <c r="DA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,46 +4171,46 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1487632771264239</v>
+        <v>-0.2831549630447726</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01139777975130363</v>
+        <v>0.1047110443098285</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.02053697068613517</v>
+        <v>-0.1370270396490442</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.009796453535939539</v>
+        <v>-0.06561766849300629</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1044470792762514</v>
+        <v>0.08675846612010144</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.08941235419648261</v>
+        <v>-0.01980260884986499</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,52 +4225,52 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.06933193973331173</v>
+        <v>-0.01633264277949773</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.001030245161517904</v>
+        <v>-0.1370064053875448</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.02605262215631136</v>
+        <v>-0.1282794951706789</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1393556000527512</v>
+        <v>-0.1515488563169343</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07232208030604852</v>
+        <v>0.185203111799694</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.09948211957468903</v>
+        <v>0.01056438942029912</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1379944878047723</v>
+        <v>-0.1677068071429713</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.07432532504634967</v>
+        <v>0.09976804626376307</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.01306958734054653</v>
+        <v>0.01735694272554248</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,106 +4306,106 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1429284511864807</v>
+        <v>-0.2265030389330226</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.05728574452149764</v>
+        <v>0.2560256141648915</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03616775326703744</v>
+        <v>-0.0415514076573648</v>
       </c>
       <c r="FC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01709616414805581</v>
+        <v>-0.1709064969026202</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1182627534924378</v>
+        <v>0.164744034266281</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.007539325529760442</v>
+        <v>0.07089589551989903</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.007155240853427771</v>
+        <v>-0.03737773774320363</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.04404318752588997</v>
+        <v>0.05481494864401702</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.0009471295030820466</v>
+        <v>0.03516099488626419</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.02108150734070569</v>
+        <v>-0.2640315116955106</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1092687541328923</v>
+        <v>0.1418915581381389</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,22 +4416,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2150578350293629</v>
+        <v>0.5409732706472929</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01645340715224021</v>
+        <v>-0.04309582758134686</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1308947601209474</v>
+        <v>-0.164762649197554</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,25 +4443,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1909418860334726</v>
+        <v>0.8476833515762414</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0140178054614115</v>
+        <v>-0.1716967580669892</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.196740857338441</v>
+        <v>-0.2282824693251076</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0360417751128238</v>
+        <v>0.2326907201693391</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,64 +4479,64 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.02772172389922653</v>
+        <v>-0.1028033155457092</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01542599144316571</v>
+        <v>-0.03083393011205577</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.04165900070002719</v>
+        <v>0.04771806699816752</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.02690986171699945</v>
+        <v>-0.4112339978691999</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.008944041364029333</v>
+        <v>-0.2030568612570967</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0181642336962472</v>
+        <v>0.1979855054677531</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02207058717779127</v>
+        <v>0.04240795101480054</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.04296436993933404</v>
+        <v>-0.1222745945212354</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,25 +4548,25 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1915880995013701</v>
+        <v>1.001987166022659</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.04081903667576706</v>
+        <v>-0.1743343349033867</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1304412385956447</v>
+        <v>-0.3489458258091452</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>-0</v>
@@ -4578,73 +4578,73 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0634589460090953</v>
+        <v>-0.05028237808533269</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.02722480978178</v>
+        <v>-0.1680078878221594</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.03547320703105214</v>
+        <v>-0.030740303839889</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.07218930227266149</v>
+        <v>0.04797708050699603</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0225240198233073</v>
+        <v>0.1379856770177644</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01887973810986917</v>
+        <v>-0.05109300434021567</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.08238613679381851</v>
+        <v>0.5691283718897604</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.01288587219781652</v>
+        <v>-0.03461557106499378</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03874005323164887</v>
+        <v>-0.1585501557556218</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,7 +4659,7 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.05372682999813318</v>
+        <v>-0.2689141884577717</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4668,52 +4668,52 @@
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01059554610538408</v>
+        <v>0.05388442612865815</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04844803970177665</v>
+        <v>0.1355455593604897</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01250994836524671</v>
+        <v>-0.5336637698696238</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01171613527048285</v>
+        <v>0.2917872567784196</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02495690536156621</v>
+        <v>0.2622562446649256</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.04238141544546808</v>
+        <v>-0.2566043124040472</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.01113765369573175</v>
+        <v>0.01977437639597956</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04947434628978348</v>
+        <v>0.1287127020368385</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.055801149694939</v>
+        <v>-0.1393000962653645</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.02681918981817489</v>
+        <v>-0.409568914377288</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0006365632438627889</v>
+        <v>0.06746480988417845</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4767,34 +4767,34 @@
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02621135989564245</v>
+        <v>-0.1329394226446696</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.009502134770895228</v>
+        <v>0.08072698742551263</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.002373259151957591</v>
+        <v>0.02912122980911021</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.03811624550060586</v>
+        <v>0.01470456531400925</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,10 +4803,10 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.02444706646769102</v>
+        <v>0.08516275516990623</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.03367442617572289</v>
+        <v>-0.1571037046451067</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4821,7 +4821,7 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.03500160317244068</v>
+        <v>-0.05796516739818667</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
@@ -4830,13 +4830,13 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.005444306543112933</v>
+        <v>-0.05957551889129262</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.03097397112601947</v>
+        <v>0.03873381374656607</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
@@ -4845,22 +4845,22 @@
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01866517939537641</v>
+        <v>-0.1166046084821691</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.0162777098814338</v>
+        <v>-0.12792757305314</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.03302400343697724</v>
+        <v>0.07141718066810351</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
@@ -4869,40 +4869,40 @@
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.04317217574984447</v>
+        <v>-0.2901841931841934</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.008032097811297795</v>
+        <v>-0.003099049293002029</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04924469714554379</v>
+        <v>0.1212018584150898</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.003723148998297417</v>
+        <v>-0.3235153755335032</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
@@ -4911,25 +4911,25 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03569640809223598</v>
+        <v>0.1459688747393665</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03829219061315533</v>
+        <v>0.0960518016856779</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.005141564379836466</v>
+        <v>-0.04938108045619978</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,28 +4938,28 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.00359831427893568</v>
+        <v>0.01624693529745101</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.04476079188392427</v>
+        <v>0.03226597112221115</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01196289187896574</v>
+        <v>-0.1240193141113997</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,13 +4968,13 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.03766721033446196</v>
+        <v>-0.004680549827872841</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -5551,19 +5551,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5505575158302849</v>
+        <v>0.02022510052521561</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1869647792384005</v>
+        <v>-0.006928703752659246</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5149652057416819</v>
+        <v>-0.005043776158198139</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4641490249175224</v>
+        <v>0.03016434642507839</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3729547018491681</v>
+        <v>-0.01808795078868428</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,34 +5599,34 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.8965998008890421</v>
+        <v>-0.01585714991556074</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3027265110431657</v>
+        <v>0.01354992844199094</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3098495136277547</v>
+        <v>-0.01256211399707556</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1606343718799428</v>
+        <v>-0.005611752085623453</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
@@ -5635,16 +5635,16 @@
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2627745170575702</v>
+        <v>-0.008983659925945839</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1669092736456806</v>
+        <v>-0.01595747955785587</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,34 +5653,34 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.2909016099233705</v>
+        <v>0.004457544016288209</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.08214723114619681</v>
+        <v>0.008785370109776536</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01021063278407631</v>
+        <v>0.000833237477156679</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.1838548351434858</v>
+        <v>5.843180636982045e-06</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.078915996136951</v>
+        <v>0.03375584578679412</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,43 +5698,43 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.5258727655075109</v>
+        <v>-0.003048157680864702</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.06336259656361527</v>
+        <v>-0.006478093018137992</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01991134648274931</v>
+        <v>-0.007083405614857153</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.3505226520307421</v>
+        <v>-0.01542995799336684</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.2956907425479152</v>
+        <v>-0.0006367791504493782</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5895519703804922</v>
+        <v>0.008044974083039181</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,16 +5752,16 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.790217025246846</v>
+        <v>0.01669144787750192</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.3115311776689687</v>
+        <v>0.006908210906927201</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,16 +5770,16 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4384984702045389</v>
+        <v>0.02526637485633385</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2468215866436242</v>
+        <v>-0.001792507805297163</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -5788,25 +5788,25 @@
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.02024926544918096</v>
+        <v>-0.008928495592916258</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1701607192030334</v>
+        <v>-0.005443243369995176</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.009825753252642134</v>
+        <v>0.003406728871171406</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,52 +5815,52 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.222154433126905</v>
+        <v>0.00338762873242641</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.4769470577926986</v>
+        <v>-0.009160314495568358</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.5214431199799255</v>
+        <v>0.01380054668107091</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.1870520545733548</v>
+        <v>0.004784185870034054</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1266707376238884</v>
+        <v>-0.005154187784140166</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.03455546703122087</v>
+        <v>0.00324593634489298</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,52 +5869,52 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.1090490024883095</v>
+        <v>0.005416920348832777</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.6576932160575604</v>
+        <v>-0.006307870613398357</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08011393211851435</v>
+        <v>0.002031922485724958</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.003695773152336445</v>
+        <v>0.000839222551930307</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1654201834111794</v>
+        <v>-0.007806018746751903</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.07160916019072465</v>
+        <v>-0.002516925216297101</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,16 +5923,16 @@
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1728890748335379</v>
+        <v>0.001308387467433841</v>
       </c>
       <c r="DV10" t="n">
         <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.02467225172215434</v>
+        <v>0.005451504590840886</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,34 +5941,34 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.06033550930618397</v>
+        <v>-0.008727386402273659</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.1901833851573926</v>
+        <v>-0.01065752905693493</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.08248764377743978</v>
+        <v>0.004080066272676445</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03422058370873715</v>
+        <v>-0.002703239886666777</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,16 +5977,16 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.2291878049697553</v>
+        <v>-0.001325835449156152</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.06178806831947702</v>
+        <v>-0.002751158608115832</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,34 +5995,34 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1521157893971231</v>
+        <v>-0.005410070747815113</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.02857731391542834</v>
+        <v>0.004811271118801269</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1155600544641937</v>
+        <v>-0.005594817808393843</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.04580836798167895</v>
+        <v>0.0005254652992898707</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,43 +6031,43 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.2046903393653886</v>
+        <v>0.005246457675171478</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.06857136971603112</v>
+        <v>-0.000462476441805401</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.1601554278660176</v>
+        <v>0.008849405761641048</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.06975352473871771</v>
+        <v>-0.004649831460195624</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.01462485073293411</v>
+        <v>-0.0009151103857993113</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,34 +6076,34 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.04005883588233029</v>
+        <v>0.002078151804504832</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.1814698235212332</v>
+        <v>0.001575405430163655</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.3608240616142978</v>
+        <v>-0.009441187358177481</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>0</v>
@@ -6112,60 +6112,60 @@
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.3300197345782492</v>
+        <v>-0.002913876902069628</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.3201069958423193</v>
+        <v>-0.2585333049876861</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6320091514483427</v>
+        <v>0.5529630661764842</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2358875639782447</v>
+        <v>-0.1370477932482038</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2234377661255625</v>
+        <v>-0.1945093181156659</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5148734774393224</v>
+        <v>0.7789314361779236</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5117548087763245</v>
+        <v>-0.1693123292857018</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,19 +6174,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02206938997238747</v>
+        <v>0.1032679108146265</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3670833177358572</v>
+        <v>0.001743118526600411</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1794759103722527</v>
+        <v>0.004585759789369774</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
@@ -6195,124 +6195,124 @@
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02078766065777697</v>
+        <v>-0.08971185440583865</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1922671714228789</v>
+        <v>-0.001805183975518334</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.07866378253460937</v>
+        <v>-0.1090909008757809</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.1146266779855946</v>
+        <v>-0.01570308135232287</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2257917011179836</v>
+        <v>0.1428413994475831</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.01182773443055132</v>
+        <v>-0.1511399933195828</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2300887619716731</v>
+        <v>-0.01714321957139878</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.7732805470806201</v>
+        <v>0.4222970165902983</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.364409427006545</v>
+        <v>-0.2647384427048711</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.212229323468509</v>
+        <v>-0.2306234121215119</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.05439842369843822</v>
+        <v>0.1254069940946709</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.4294288674343181</v>
+        <v>0.004804474852922525</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.09121987303078703</v>
+        <v>0.08064405063759986</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1449943613813964</v>
+        <v>0.2220026589409974</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.4038474477770921</v>
+        <v>0.171720570171432</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,49 +6336,49 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.1237834296615499</v>
+        <v>0.08834896839037557</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4173557391239679</v>
+        <v>0.3337209369970852</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.04247553644818637</v>
+        <v>-0.04612030204306114</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.05826561555414225</v>
+        <v>0.08881032044358303</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.134598138210163</v>
+        <v>-0.2173739381412612</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.007093524758107107</v>
+        <v>0.02342894875153484</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
@@ -6390,76 +6390,76 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.3061325532497021</v>
+        <v>-0.06029070960127137</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.1297606980549161</v>
+        <v>-0.4038189852821087</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.3414984320443166</v>
+        <v>-0.04281033032491656</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.02728733132185802</v>
+        <v>0.07510496898136709</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1509163342354331</v>
+        <v>-0.2256094123070137</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0227652766982379</v>
+        <v>-0.01524980823592633</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.3088086672933626</v>
+        <v>0.1058392357186666</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.5213418263506325</v>
+        <v>-0.3568024217822677</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06216853613195463</v>
+        <v>0.0001495289018542181</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.1754732522984578</v>
+        <v>-0.05700532481184557</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.2226355621161783</v>
+        <v>-0.1525280825747158</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
@@ -6483,25 +6483,25 @@
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.05583095638048067</v>
+        <v>-0.01968677114993017</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.05755652401285949</v>
+        <v>0.1938920910948649</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1397478414711541</v>
+        <v>0.1256952038676695</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,25 +6510,25 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.1211244249335567</v>
+        <v>0.05184435047691616</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.07579577565637186</v>
+        <v>-0.007783920749178976</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.19335791219972</v>
+        <v>-0.1357277643634022</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01535623056011122</v>
+        <v>-0.0495159243981384</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6552,19 +6552,19 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0.03335098049438633</v>
+        <v>-0.09253197567582172</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1115873081619997</v>
+        <v>-0.1382640812294951</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.03931680993140869</v>
+        <v>-0.02106927144955822</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6576,13 +6576,13 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.05307678637330294</v>
+        <v>0.07933568119763411</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.139754193369757</v>
+        <v>-0.2781996045761439</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,25 +6591,25 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.0501612256633138</v>
+        <v>-0.02736578918901152</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.1945824355983657</v>
+        <v>0.07077275099166266</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.08902586162004682</v>
+        <v>0.01281679223584149</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.08871961031104381</v>
+        <v>0.08655807250323579</v>
       </c>
       <c r="FL11" t="n">
         <v>0</v>
@@ -6633,37 +6633,37 @@
         <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.003265344563816009</v>
+        <v>-0.09611510256817225</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.03363000358762867</v>
+        <v>0.02815750246456566</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01053009293721037</v>
+        <v>0.04915292261915805</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.07931406167625607</v>
+        <v>0.04615210544553407</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.1912028072345067</v>
+        <v>-0.1910668739422346</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6675,7 +6675,7 @@
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,49 +6692,49 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6394727265793381</v>
+        <v>0.1515170800182909</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2867283245309152</v>
+        <v>-0.1785828054220088</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3522750555858268</v>
+        <v>-0.1529373627829677</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4484784375792149</v>
+        <v>0.2332934832050888</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3085273774915624</v>
+        <v>-0.1899268769631863</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3103309998831958</v>
+        <v>-0.2066543347703509</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6746,49 +6746,49 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2111122096653329</v>
+        <v>0.0373481744772048</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.260498669818286</v>
+        <v>-0.05229556296700465</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.04222317993537852</v>
+        <v>0.06478719294918348</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2368052384134104</v>
+        <v>-0.09351317470368595</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.07470035197579998</v>
+        <v>-0.180204740810824</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.02747525251334188</v>
+        <v>0.02957065424390622</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,10 +6797,10 @@
         <v>-0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.07382749035709109</v>
+        <v>0.1439516651590127</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
@@ -6809,16 +6809,16 @@
         <v>-0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.01421597102856941</v>
+        <v>0.03010748215956065</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.08088867344575527</v>
+        <v>0.04590629885091129</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.7111857861412095</v>
+        <v>0.4021916197562682</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,40 +6836,40 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.01144157846163145</v>
+        <v>-0.005874328122446166</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.194743821901728</v>
+        <v>0.009625491348965206</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1386630283508359</v>
+        <v>-0.1451944011056095</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1537017720514165</v>
+        <v>-0.1910272237340425</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.1719667992132358</v>
+        <v>-0.07176677171514768</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.129921773323781</v>
+        <v>-0.01045616499857672</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.2753612797122582</v>
+        <v>0.1159085671766333</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.05320709510504697</v>
+        <v>0.0861933956422469</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,34 +6908,34 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2612426899628142</v>
+        <v>0.2330073090554946</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.0256976584708545</v>
+        <v>-0.03630570722091228</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.05610276921408027</v>
+        <v>0.004564153819095945</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1634144912905043</v>
+        <v>-0.06216006196294081</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
@@ -6944,13 +6944,13 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.04919595272246327</v>
+        <v>0.05979204259414948</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0819156380931783</v>
+        <v>0.01955000856643379</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.2291046544859701</v>
+        <v>-0.179750774142917</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1671749971551101</v>
+        <v>0.09763531737393522</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.007678939358759736</v>
+        <v>-0.1293977393322897</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,10 +6986,10 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1318684575569194</v>
+        <v>-0.06370295787895482</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.04670968884100793</v>
+        <v>0.06014662710045873</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.07954506941689378</v>
+        <v>0.03223899505241039</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7013,52 +7013,52 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.4164543422767302</v>
+        <v>-0.08455966312271353</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04491044981547947</v>
+        <v>0.01159521707168701</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.1382195987126834</v>
+        <v>-0.05588306133124435</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.07751523479649475</v>
+        <v>-0.02926145622109126</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.06365130329668778</v>
+        <v>0.122487145166994</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0.01293864051259389</v>
+        <v>0.0681238186543313</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
@@ -7067,52 +7067,52 @@
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1439916073538324</v>
+        <v>0.02126601434875945</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.09670330927506753</v>
+        <v>-0.07216024440151905</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>-0.006568243495610016</v>
+        <v>-0.002395241609161545</v>
       </c>
       <c r="ED12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.05240041749899019</v>
+        <v>-0.06448903457779688</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.09775697819205766</v>
+        <v>0.005616051653930747</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.1027576022496439</v>
+        <v>-0.02655364625365641</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,52 +7121,52 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.06806216159196697</v>
+        <v>-0.03691582877280806</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.006981400744815148</v>
+        <v>0.003320796803728783</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0.01194485847981911</v>
+        <v>-0.04974128842587698</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1408571109494271</v>
+        <v>-0.06719123244635244</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.04427624392009453</v>
+        <v>0.04232915060041374</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.07958314407140828</v>
+        <v>0.01495462210776252</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,25 +7175,25 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.04479719748852456</v>
+        <v>-0.06034077897986307</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.1205907842430766</v>
+        <v>-0.02986971132053118</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.05932030006412938</v>
+        <v>-0.03485937829643673</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7202,10 +7202,10 @@
         <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01015269760119976</v>
+        <v>-0.02947742660749332</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,28 +7214,28 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02256102689127081</v>
+        <v>-0.01428312124510887</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0001663203915489765</v>
+        <v>0.09597184008323505</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.1106901193209862</v>
+        <v>-0.07249558774204581</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,10 +7244,10 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>-0.06442879973015084</v>
+        <v>0.06998418932270901</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
@@ -7258,10 +7258,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>1.109002510642023</v>
+        <v>0.8057382917230139</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3620317104367999</v>
+        <v>-0.4576070314345054</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5441075947901269</v>
+        <v>-0.1858729010367829</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8208495368911543</v>
+        <v>1.042385439110252</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,115 +7297,115 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3815344216259309</v>
+        <v>-0.5267790538272202</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.4957252327836016</v>
+        <v>-0.1679277293185162</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.343785183382271</v>
+        <v>0.09299445850552605</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03604885916899599</v>
+        <v>-0.2032318721017696</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.1046669798180174</v>
+        <v>-0.181649749038749</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3276670619599004</v>
+        <v>0.103616847664272</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.08144003468929426</v>
+        <v>-0.2032451122506458</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.02599383779852389</v>
+        <v>0.01503392782587149</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1728023585219027</v>
+        <v>0.2755197080713718</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.005978002587623073</v>
+        <v>0.07529302089585101</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.03660857206532703</v>
+        <v>-0.03901436954808084</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.064637479373003</v>
+        <v>1.104277197311176</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.08634485769827283</v>
+        <v>-0.1716910971726517</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.3078297614297999</v>
+        <v>-0.002469566189113378</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1780003823063034</v>
+        <v>-0.1516723463170842</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.3603540251150389</v>
+        <v>-0.2444420471881887</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7441,16 +7441,16 @@
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.2575292020879729</v>
+        <v>-0.05346438511276832</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1226796082448601</v>
+        <v>0.1237868246197611</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,25 +7459,25 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.432846132630344</v>
+        <v>0.2446556712175755</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0.009489365849392245</v>
+        <v>0.109805446704583</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.546285728803616</v>
+        <v>0.5693032835191646</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,25 +7486,25 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.08227314981920483</v>
+        <v>-0.1996224939744918</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.1041760068704934</v>
+        <v>-0.1662091553644489</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.2590944111098931</v>
+        <v>-0.3543258058344872</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,37 +7513,37 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01560623151484463</v>
+        <v>0.1056803976698626</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.1839378920199971</v>
+        <v>0.07741826415011485</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.3250856545392993</v>
+        <v>-0.6245055263053634</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.2970223661660355</v>
+        <v>0.03607912319416406</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,49 +7552,49 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.06131974582781816</v>
+        <v>0.008200972626623452</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.2241515681933035</v>
+        <v>-0.3382672069974696</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.02473182254519969</v>
+        <v>0.0850783579599108</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.1406341338322815</v>
+        <v>0.09133186133101216</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.5652883986343037</v>
+        <v>-0.2235119059635537</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1323822313163398</v>
+        <v>-0.01829276429577338</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,22 +7606,22 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.04357367690794176</v>
+        <v>-0.05770101523973345</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.1446952456697684</v>
+        <v>-0.1665589537826136</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.006620924120542991</v>
+        <v>0.05170368488937838</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,16 +7630,16 @@
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.03017930374928252</v>
+        <v>-0.1805678711344889</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1879251761322843</v>
+        <v>0.2571191806937556</v>
       </c>
       <c r="DY13" t="n">
         <v>-0</v>
@@ -7648,79 +7648,79 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.09381227894990062</v>
+        <v>-0.07204335158484623</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0134657610443933</v>
+        <v>0.2208004499992672</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03188525121688013</v>
+        <v>-0.1679226203046627</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.06467700355726905</v>
+        <v>0.00297280947644209</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.2407440500675926</v>
+        <v>0.04955186829153677</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1636879045420602</v>
+        <v>-0.1867660784185236</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.03115582351661013</v>
+        <v>0.04020943626790926</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.02288997964432253</v>
+        <v>0.1321742322290466</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.2604506133485941</v>
+        <v>-0.3976481536409839</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,100 +7729,100 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.005492865132659888</v>
+        <v>0.06586781392941472</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.1301566168033032</v>
+        <v>0.1026163733690383</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.122680146768897</v>
+        <v>-0.1395023988703115</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.1038613188688495</v>
+        <v>-0.01866983865406524</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.1520485817299997</v>
+        <v>-0.08742228420918922</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01495981794070308</v>
+        <v>-0.01527578241722053</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01107967561369109</v>
+        <v>0.03631628878809224</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.05630249728732539</v>
+        <v>-0.0133430283011477</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.2659828494227312</v>
+        <v>-0.1899075366752729</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.0553870713158484</v>
+        <v>0.008725589054809592</v>
       </c>
     </row>
     <row r="14">
@@ -8399,16 +8399,16 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.5263589242471366</v>
+        <v>-0.5631578618896709</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6561602907780183</v>
+        <v>0.2732706334145816</v>
       </c>
       <c r="D15" t="n">
         <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1462611492574238</v>
+        <v>0.2674470399554658</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -8426,19 +8426,19 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4469623166147181</v>
+        <v>-0.6941938154356907</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4752960060020092</v>
+        <v>0.2824808025072283</v>
       </c>
       <c r="M15" t="n">
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5022363781143702</v>
+        <v>0.2494001338071679</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -8450,19 +8450,19 @@
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1772453957995592</v>
+        <v>-0.1142947920595935</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.02177110209064688</v>
+        <v>-0.07327817311306169</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.05584199838317818</v>
+        <v>-0.03353824052204277</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8471,79 +8471,79 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.248185614094744</v>
+        <v>-0.02623212539862257</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.02456346957911471</v>
+        <v>0.1407817637722961</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.1937193304210485</v>
+        <v>0.01496337777619614</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.2748260904433181</v>
+        <v>-0.2043247819273134</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0955866649607692</v>
+        <v>0.02024014149231052</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02093089353460846</v>
+        <v>-0.223362240804027</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.6665477772920931</v>
+        <v>-0.6372113743753836</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.4128272211552594</v>
+        <v>0.01783535048790851</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.1544546201947827</v>
+        <v>0.04227646938157681</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
@@ -8552,7 +8552,7 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
@@ -8561,16 +8561,16 @@
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.01510141920161883</v>
+        <v>0.2579796255570939</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.2102066447069666</v>
+        <v>0.2094293480203513</v>
       </c>
       <c r="BF15" t="n">
         <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.5684338243253173</v>
+        <v>0.2936535794859261</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
@@ -8588,22 +8588,22 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.1577480301074134</v>
+        <v>0.03496683066462872</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.0842575046735657</v>
+        <v>-0.01942164198606022</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.3468793253000507</v>
+        <v>0.003445786322469074</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
@@ -8615,19 +8615,19 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.1960200829614315</v>
+        <v>-0.3748113828984223</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.3169478564083854</v>
+        <v>0.01710225989311437</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.05198104557020931</v>
+        <v>0.003601708479361075</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -8639,19 +8639,19 @@
         <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1217406627379084</v>
+        <v>0.257226405601484</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0.05553385505954265</v>
+        <v>-0.08536356688920306</v>
       </c>
       <c r="CG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.05840003207354124</v>
+        <v>-0.0455146348700882</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,16 +8669,16 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0711566276155803</v>
+        <v>0.3372475537344869</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0.01888796609448625</v>
+        <v>-0.07694899926479708</v>
       </c>
       <c r="CP15" t="n">
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.2129079523229254</v>
+        <v>-0.1096120757069551</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
@@ -8687,25 +8687,25 @@
         <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.07697652879253047</v>
+        <v>0.2421206035954034</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0.06853611783316689</v>
+        <v>-0.06827791247726911</v>
       </c>
       <c r="CY15" t="n">
         <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.07306996379440737</v>
+        <v>-0.04127070921722357</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
@@ -8714,7 +8714,7 @@
         <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>-0</v>
@@ -8723,73 +8723,73 @@
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.202821078365236</v>
+        <v>0.07019791562354652</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.05982553087285746</v>
+        <v>-0.04057503848845449</v>
       </c>
       <c r="DH15" t="n">
         <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1601148250253166</v>
+        <v>0.01972755220594033</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.01590764248874078</v>
+        <v>0.1378029806118728</v>
       </c>
       <c r="DP15" t="n">
-        <v>-0.1468291164307829</v>
+        <v>-0.07757313147299982</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.08027537761310356</v>
+        <v>0.001172583039864709</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.01492008710118048</v>
+        <v>-0.1469649384969493</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.2141407255741934</v>
+        <v>-0.05591836991055507</v>
       </c>
       <c r="DZ15" t="n">
         <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.03275142293197108</v>
+        <v>0.06442700053325329</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
@@ -8801,19 +8801,19 @@
         <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.02751634740164072</v>
+        <v>0.1743412624761679</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0.01088212341903618</v>
+        <v>0.07020859540515499</v>
       </c>
       <c r="EI15" t="n">
         <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.1320169680259974</v>
+        <v>-0.04876339128998497</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
@@ -8831,52 +8831,52 @@
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.07524382686824914</v>
+        <v>0.1734197179600232</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.06860221017485242</v>
+        <v>0.01883251155506685</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.1268866366518944</v>
+        <v>-0.06660686884642783</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
         <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.09343948052611313</v>
+        <v>0.2895237534027905</v>
       </c>
       <c r="EZ15" t="n">
-        <v>-0.05612614776440268</v>
+        <v>-0.07437047190047702</v>
       </c>
       <c r="FA15" t="n">
         <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.08105116936126079</v>
+        <v>-0.05918123598659694</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
@@ -8885,90 +8885,90 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.1519325408030751</v>
+        <v>0.06187777404642715</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1905831366988929</v>
+        <v>0.1218828352101071</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.1886199290958864</v>
+        <v>0.1175291277334836</v>
       </c>
       <c r="FL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-1.264573956750177e-05</v>
+        <v>0.001619905656652519</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0.0773749085844959</v>
+        <v>-0.0002143237558384262</v>
       </c>
       <c r="FS15" t="n">
         <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.006970377742108164</v>
+        <v>-0.009797689040986993</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
         <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.003959591714771491</v>
+        <v>0.148512724741184</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.07444906610766343</v>
+        <v>0.113605793512404</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.4193913524864991</v>
+        <v>-0.1760098734128454</v>
       </c>
       <c r="C16" t="n">
         <v>-0</v>
@@ -8977,13 +8977,13 @@
         <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05735580291277353</v>
+        <v>0.05108108844583922</v>
       </c>
       <c r="F16" t="n">
-        <v>1.035147378343664</v>
+        <v>0.3398388795887985</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -8992,10 +8992,10 @@
         <v>-0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3519979926276593</v>
+        <v>-0.2277580473879689</v>
       </c>
       <c r="L16" t="n">
         <v>-0</v>
@@ -9004,25 +9004,25 @@
         <v>-0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.09719004825977103</v>
+        <v>0.1447550812273173</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7970956499911807</v>
+        <v>0.4432223597338499</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.03687451535882046</v>
+        <v>-0.07309131683258129</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,13 +9031,13 @@
         <v>-0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1586308321541925</v>
+        <v>0.06205921821999616</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0933737787487529</v>
+        <v>0.09502427196030597</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -9046,22 +9046,22 @@
         <v>-0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.05761432983598488</v>
+        <v>0.02209219360342318</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0562873858139684</v>
+        <v>0.1551542764489358</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.05388466812728854</v>
+        <v>-0.0196039151966622</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9070,13 +9070,13 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK16" t="n">
         <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.02929476488184719</v>
+        <v>-0.0347775688400293</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01413938302415433</v>
+        <v>-0.00591116684673616</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.1717182657779255</v>
+        <v>0.07993475310292625</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -9100,37 +9100,37 @@
         <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.3856684663823999</v>
+        <v>-0.4746227102226953</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
         <v>-0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.2701084146152701</v>
+        <v>0.113871784394312</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.7171740509332811</v>
+        <v>0.2673083526080413</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.1219493344531752</v>
+        <v>0.1293530938500242</v>
       </c>
       <c r="BE16" t="n">
         <v>-0</v>
@@ -9139,10 +9139,10 @@
         <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.04847327529219924</v>
+        <v>0.04781527348638306</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.1385884201723515</v>
+        <v>0.002477034467663897</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
@@ -9151,52 +9151,52 @@
         <v>0</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0.1830357960083081</v>
+        <v>-0.08663745212382837</v>
       </c>
       <c r="BN16" t="n">
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.06522403184129982</v>
+        <v>-0.05998477186128948</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.06617832325918234</v>
+        <v>-0.02928035250940444</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
         <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0.146696166919964</v>
+        <v>-0.1381189772854395</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>-0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.09210515393069182</v>
+        <v>0.03099274849493336</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.3471341093134395</v>
+        <v>0.1776270354316332</v>
       </c>
       <c r="CA16" t="n">
         <v>0</v>
@@ -9205,40 +9205,40 @@
         <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.1194684396780524</v>
+        <v>0.08918075099011855</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.01869627851348746</v>
+        <v>-0.04216184501575252</v>
       </c>
       <c r="CI16" t="n">
-        <v>-0.160687091430458</v>
+        <v>-0.06515636968803766</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>-0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
         <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.005543524447955893</v>
+        <v>0.0943336086765339</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -9247,16 +9247,16 @@
         <v>0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.2375529704357506</v>
+        <v>-0.09981970475303394</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.03067271553226303</v>
+        <v>-0.04909760105272534</v>
       </c>
       <c r="CS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU16" t="n">
         <v>0</v>
@@ -9265,73 +9265,73 @@
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.09086067261758959</v>
+        <v>0.0789224294932242</v>
       </c>
       <c r="CX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY16" t="n">
         <v>-0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.01162367555539271</v>
+        <v>-0.04690765775715289</v>
       </c>
       <c r="DA16" t="n">
-        <v>-0.1696518128706331</v>
+        <v>-0.09382844649885944</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC16" t="n">
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.1257059367863718</v>
+        <v>0.07301724956976149</v>
       </c>
       <c r="DG16" t="n">
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.2932217290319694</v>
+        <v>0.1042843860815658</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.007581230313567193</v>
+        <v>-0.01795522942630319</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.02834621083858908</v>
+        <v>-0.05633355891906135</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.05154513664228862</v>
+        <v>0.05769492578151223</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.06521450546557701</v>
+        <v>-0.08392929455942352</v>
       </c>
       <c r="DT16" t="n">
         <v>0</v>
@@ -9340,13 +9340,13 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.09323359104688517</v>
+        <v>0.1038601844819852</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,10 +9355,10 @@
         <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.07898271216613939</v>
+        <v>0.00107141392389684</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.1188386473744737</v>
+        <v>0.01934445134179449</v>
       </c>
       <c r="EC16" t="n">
         <v>0</v>
@@ -9367,31 +9367,31 @@
         <v>-0</v>
       </c>
       <c r="EE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF16" t="n">
         <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0637277564739325</v>
+        <v>0.06948229255083882</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.02096748542565594</v>
+        <v>-0.06157488572586131</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0.1142137547457192</v>
+        <v>0.02630154983530177</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>0</v>
@@ -9400,73 +9400,73 @@
         <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.07538477723198488</v>
+        <v>0.04945185436363656</v>
       </c>
       <c r="EQ16" t="n">
         <v>0</v>
       </c>
       <c r="ER16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.05016986799317925</v>
+        <v>-0.04407372845362763</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.04148253538983084</v>
+        <v>0.03989663103855391</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
         <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.08269910872492069</v>
+        <v>0.1000331103532043</v>
       </c>
       <c r="EZ16" t="n">
         <v>0</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.03558840908236152</v>
+        <v>-0.0178894925286274</v>
       </c>
       <c r="FC16" t="n">
-        <v>-0.1572501519018988</v>
+        <v>-0.08064123985832243</v>
       </c>
       <c r="FD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.007814731657287362</v>
+        <v>-0.07691670110214546</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.04383720571030961</v>
+        <v>-0.001812324568310594</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.1399684100677052</v>
+        <v>-0.1279575096372529</v>
       </c>
       <c r="FM16" t="n">
         <v>-0</v>
@@ -9475,31 +9475,31 @@
         <v>0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
         <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.003516116555176326</v>
+        <v>0.02803476455159675</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.08088923460527922</v>
+        <v>-0.07429806703954973</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0.1594481572666532</v>
+        <v>0.1028504445231461</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
         <v>-0</v>
@@ -9508,19 +9508,19 @@
         <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.04086205755550364</v>
+        <v>0.05567520023880203</v>
       </c>
       <c r="GA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.07005114483952433</v>
+        <v>-0.04728610900655472</v>
       </c>
       <c r="GE16" t="n">
         <v>0</v>
